--- a/docs/ЗАДАНИЯ — награды-пары (22.09.2026).xlsx
+++ b/docs/ЗАДАНИЯ — награды-пары (22.09.2026).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Задания" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Баланс и правила" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Задания" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Баланс и правила" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -611,7 +611,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1 трофей</t>
+          <t>1 трофей + спец-действие</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       <c r="D7" s="2" t="inlineStr"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>ДВА СПЕЦ-ДЕЙСТВИЯ</t>
+          <t>ТРИ СПЕЦ-ДЕЙСТВИЯ</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Два неоткрытых контейнера сданы. Награда — два спец-действия: вскрыть следующие или сыграть карту.</t>
+          <t>Усиления у карты нет, поэтому награда — сразу три спец-действия (решение 22.09).</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>ДВА СПЕЦ-ДЕЙСТВИЯ</t>
+          <t>Снаряжение ИЛИ Рынок</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Разработка + Приобретения</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Ты вернул два войска в запас — освободил и место, и жетоны. Награда — два спец-действия: цепочка карт вместо возни на поле.</t>
+          <t>Ты убрал войска с поля. Дожать — Снаряжение: нанять заново, где нужно. Уйти — Рынок. ПРЕДЛОЖЕНИЕ 22.09 вместо двух спец-действий.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1 трофей</t>
+          <t>1 трофей + спец-действие</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1 трофей</t>
+          <t>1 трофей + спец-действие</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>ТРЕБУЕТ РЕШЕНИЯ: условие есть, награды нет</t>
+          <t>1 трофей + спец-действие</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ДВА СПЕЦ-ДЕЙСТВИЯ</t>
+          <t>Манёвр ИЛИ Стройка</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Наступление + Инфраструктура</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Ты снёс жетон у того, кто богаче тебя зданиями. Награда — два спец-действия: разогнать цепочку, пока он не ответил.</t>
+          <t>Ты ударил по богатому. Дожать — Манёвр: войти в пролом. Уйти — Стройка: закрепиться. Боя нет — им карта закрывается. ПРЕДЛОЖЕНИЕ 22.09.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1 трофей</t>
+          <t>1 трофей + спец-действие</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1619,22 +1619,22 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ДВА СПЕЦ-ДЕЙСТВИЯ</t>
+          <t>Снаряжение ИЛИ Наука</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Разработка + Приобретения</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1 трофей</t>
+          <t>1 трофей + спец-действие</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Ты снёс жетон у более богатого соперника. Награда — два спец-действия.</t>
+          <t>То же условие, что у «Первой крови», другой исход. Дожать — Снаряжение: восполнить потери. Уйти — Наука: пустить трофей в дело. ПРЕДЛОЖЕНИЕ 22.09.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1666,22 +1666,22 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>ДВА СПЕЦ-ДЕЙСТВИЯ</t>
+          <t>Бой ИЛИ Добыча</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Наступление + Разработка</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1 трофей</t>
+          <t>1 трофей + спец-действие</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Запас одного рода пуст — ты выложил на поле всё. Награда — два спец-действия: на поле места нет, играй картами.</t>
+          <t>Все войска рода на поле. Дожать — Бой: пустить их в дело. Уйти — Добыча. ПРЕДЛОЖЕНИЕ 22.09.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1 трофей</t>
+          <t>1 трофей + спец-действие</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1 трофей</t>
+          <t>1 трофей + спец-действие</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1 трофей</t>
+          <t>1 трофей + спец-действие</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1 трофей</t>
+          <t>1 трофей + спец-действие</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="92" customWidth="1" min="1" max="1"/>
@@ -2369,7 +2369,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -2429,7 +2429,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2439,9 +2439,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
-      </c>
-    </row>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
@@ -2512,9 +2513,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
@@ -2522,9 +2521,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -2535,49 +2532,96 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  o20 «Коммутация» — есть усиленное условие, нет усиленной награды.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  o12 и o15 — одинаковое базовое условие («построй 2 здания на разных гексах»).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  o34 и o64 — одинаковое условие («трофеи тремя разными способами»).</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  o70 и o71 — одинаковое условие («2 чужих жетона среди уничтоженных»).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  o21 и o43 — одинаковое условие («снеси жетон у более богатого зданиями»).</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">  o20 «Коммутация» (два источника с ровно одним свободным кубиком) — РЕШЕНО 22.09: 1 трофей + спец-действие.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  o10, o21, o43, o63 — два спец-действия в базе И спец-действие за усиление:</t>
+          <t xml:space="preserve">  РЕШЕНО 22.09: два спец-действия в основной награде убраны у карт с усилением; у o10, o21, o43, o63 — пары действий (предложение).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">     итого три спец-действия с одной карты.</t>
+          <t xml:space="preserve">  Одинаковые условия (o12/o15, o34/o64, o70/o71, o21/o43) — ОСТАВЛЕНЫ, так задумано.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ОБЯЗАТЕЛЬСТВО АВТОРА (22.09.2026) — не правило игры, решение по наградам:</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  если усиленная награда — один ресурс (1 трофей, 1 жетон модуля, 1 карта арсенала),</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  к ней добавляется спец-действие. Спец-действие из награды можно разыграть после</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  действия основной награды — отсюда цепочки заданий за один ход.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Применено: все «1 трофей» стали «1 трофей + спец-действие» (11 карт с o20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>СПЕЦ-ДЕЙСТВИЯ В НАГРАДАХ (22.09.2026, обязательство автора, не правило игры):</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • основная награда из спец-действий — только у карт БЕЗ усиления, и сразу три;</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    не каждая карта без усиления её получает;</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • иначе спец-действие приходит только в усиленной награде из одного ресурса.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Двойной ресурс бывает только двух видов: 2 карты арсенала или 2 трофея.</t>
         </is>
       </c>
     </row>
